--- a/data/screener/TCS.xlsx
+++ b/data/screener/TCS.xlsx
@@ -4054,7 +4054,7 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>2559.20</v>
+        <v>2285.00</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -4062,7 +4062,7 @@
         <v>79</v>
       </c>
       <c r="B9">
-        <v>926071.97</v>
+        <v>826733.07</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -4075,34 +4075,34 @@
         <v>38</v>
       </c>
       <c r="B16" s="16">
-        <v>42460.0</v>
+        <v>42825.0</v>
       </c>
       <c r="C16" s="16">
-        <v>42825.0</v>
+        <v>43190.0</v>
       </c>
       <c r="D16" s="16">
-        <v>43190.0</v>
+        <v>43555.0</v>
       </c>
       <c r="E16" s="16">
-        <v>43555.0</v>
+        <v>43921.0</v>
       </c>
       <c r="F16" s="16">
-        <v>43921.0</v>
+        <v>44286.0</v>
       </c>
       <c r="G16" s="16">
-        <v>44286.0</v>
+        <v>44651.0</v>
       </c>
       <c r="H16" s="16">
-        <v>44651.0</v>
+        <v>45016.0</v>
       </c>
       <c r="I16" s="16">
-        <v>45016.0</v>
+        <v>45382.0</v>
       </c>
       <c r="J16" s="16">
-        <v>45382.0</v>
+        <v>45747.0</v>
       </c>
       <c r="K16" s="16">
-        <v>45747.0</v>
+        <v>46112.0</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4110,73 +4110,76 @@
         <v>6</v>
       </c>
       <c r="B17">
-        <v>108646.0</v>
+        <v>117966.0</v>
       </c>
       <c r="C17">
-        <v>117966.0</v>
+        <v>123104.0</v>
       </c>
       <c r="D17">
-        <v>123104.0</v>
+        <v>146463.0</v>
       </c>
       <c r="E17">
-        <v>146463.0</v>
+        <v>156949.0</v>
       </c>
       <c r="F17">
-        <v>156949.0</v>
+        <v>164177.0</v>
       </c>
       <c r="G17">
-        <v>164177.0</v>
+        <v>191754.0</v>
       </c>
       <c r="H17">
-        <v>191754.0</v>
+        <v>225458.0</v>
       </c>
       <c r="I17">
-        <v>225458.0</v>
+        <v>240893.0</v>
       </c>
       <c r="J17">
-        <v>240893.0</v>
+        <v>255324.0</v>
       </c>
       <c r="K17">
-        <v>255324.0</v>
+        <v>267021.0</v>
       </c>
     </row>
     <row r="18" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>80</v>
       </c>
+      <c r="B18">
+        <v>94.0</v>
+      </c>
       <c r="C18">
-        <v>94.0</v>
+        <v>86.0</v>
       </c>
       <c r="D18">
-        <v>86.0</v>
+        <v>40.0</v>
       </c>
       <c r="E18">
-        <v>40.0</v>
+        <v>18.0</v>
       </c>
       <c r="F18">
-        <v>18.0</v>
+        <v>14.0</v>
       </c>
       <c r="G18">
-        <v>14.0</v>
+        <v>29.0</v>
       </c>
       <c r="H18">
-        <v>29.0</v>
+        <v>37.0</v>
       </c>
       <c r="I18">
-        <v>37.0</v>
+        <v>42.0</v>
       </c>
       <c r="J18">
-        <v>42.0</v>
+        <v>49.0</v>
       </c>
       <c r="K18">
-        <v>49.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C19">
+      <c r="B19">
         <v>1.0</v>
       </c>
     </row>
@@ -4190,34 +4193,34 @@
         <v>83</v>
       </c>
       <c r="B21">
-        <v>2571.0</v>
+        <v>2715.0</v>
       </c>
       <c r="C21">
-        <v>2715.0</v>
+        <v>2614.0</v>
       </c>
       <c r="D21">
-        <v>2614.0</v>
+        <v>2230.0</v>
       </c>
       <c r="E21">
-        <v>2230.0</v>
+        <v>1887.0</v>
       </c>
       <c r="F21">
-        <v>1887.0</v>
+        <v>1448.0</v>
       </c>
       <c r="G21">
-        <v>1448.0</v>
+        <v>1134.0</v>
       </c>
       <c r="H21">
-        <v>1134.0</v>
+        <v>1844.0</v>
       </c>
       <c r="I21">
-        <v>1844.0</v>
+        <v>3660.0</v>
       </c>
       <c r="J21">
-        <v>3660.0</v>
+        <v>11599.0</v>
       </c>
       <c r="K21">
-        <v>11599.0</v>
+        <v>4356.0</v>
       </c>
     </row>
     <row r="22" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4225,34 +4228,34 @@
         <v>84</v>
       </c>
       <c r="B22">
-        <v>55348.0</v>
+        <v>61621.0</v>
       </c>
       <c r="C22">
-        <v>61621.0</v>
+        <v>66396.0</v>
       </c>
       <c r="D22">
-        <v>66396.0</v>
+        <v>78246.0</v>
       </c>
       <c r="E22">
-        <v>78246.0</v>
+        <v>85952.0</v>
       </c>
       <c r="F22">
-        <v>85952.0</v>
+        <v>91814.0</v>
       </c>
       <c r="G22">
-        <v>91814.0</v>
+        <v>107554.0</v>
       </c>
       <c r="H22">
-        <v>107554.0</v>
+        <v>127522.0</v>
       </c>
       <c r="I22">
-        <v>127522.0</v>
+        <v>140131.0</v>
       </c>
       <c r="J22">
-        <v>140131.0</v>
+        <v>145788.0</v>
       </c>
       <c r="K22">
-        <v>145788.0</v>
+        <v>154994.0</v>
       </c>
     </row>
     <row r="23" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4260,34 +4263,34 @@
         <v>85</v>
       </c>
       <c r="B23">
-        <v>15589.0</v>
+        <v>16392.0</v>
       </c>
       <c r="C23">
-        <v>16392.0</v>
+        <v>16808.0</v>
       </c>
       <c r="D23">
-        <v>16808.0</v>
+        <v>20387.0</v>
       </c>
       <c r="E23">
-        <v>20387.0</v>
+        <v>20527.0</v>
       </c>
       <c r="F23">
-        <v>20527.0</v>
+        <v>18322.0</v>
       </c>
       <c r="G23">
-        <v>18322.0</v>
+        <v>23187.0</v>
       </c>
       <c r="H23">
-        <v>23187.0</v>
+        <v>28913.0</v>
       </c>
       <c r="I23">
-        <v>28913.0</v>
+        <v>24151.0</v>
       </c>
       <c r="J23">
-        <v>24151.0</v>
+        <v>20729.0</v>
       </c>
       <c r="K23">
-        <v>20729.0</v>
+        <v>24434.0</v>
       </c>
     </row>
     <row r="24" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4295,34 +4298,34 @@
         <v>86</v>
       </c>
       <c r="B24">
-        <v>4461.0</v>
+        <v>4834.0</v>
       </c>
       <c r="C24">
-        <v>4834.0</v>
+        <v>4684.0</v>
       </c>
       <c r="D24">
-        <v>4684.0</v>
+        <v>6054.0</v>
       </c>
       <c r="E24">
-        <v>6054.0</v>
+        <v>6456.0</v>
       </c>
       <c r="F24">
-        <v>6456.0</v>
+        <v>6033.0</v>
       </c>
       <c r="G24">
-        <v>6033.0</v>
+        <v>6793.0</v>
       </c>
       <c r="H24">
-        <v>6793.0</v>
+        <v>7883.0</v>
       </c>
       <c r="I24">
-        <v>7883.0</v>
+        <v>8613.0</v>
       </c>
       <c r="J24">
-        <v>8613.0</v>
+        <v>9752.0</v>
       </c>
       <c r="K24">
-        <v>9752.0</v>
+        <v>10796.0</v>
       </c>
     </row>
     <row r="25" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4330,34 +4333,34 @@
         <v>9</v>
       </c>
       <c r="B25">
-        <v>3084.0</v>
+        <v>4221.0</v>
       </c>
       <c r="C25">
-        <v>4221.0</v>
+        <v>3642.0</v>
       </c>
       <c r="D25">
-        <v>3642.0</v>
+        <v>4311.0</v>
       </c>
       <c r="E25">
-        <v>4311.0</v>
+        <v>4592.0</v>
       </c>
       <c r="F25">
-        <v>4592.0</v>
+        <v>1916.0</v>
       </c>
       <c r="G25">
-        <v>1916.0</v>
+        <v>4018.0</v>
       </c>
       <c r="H25">
-        <v>4018.0</v>
+        <v>3449.0</v>
       </c>
       <c r="I25">
-        <v>3449.0</v>
+        <v>3464.0</v>
       </c>
       <c r="J25">
-        <v>3464.0</v>
+        <v>3962.0</v>
       </c>
       <c r="K25">
-        <v>3962.0</v>
+        <v>-124.0</v>
       </c>
     </row>
     <row r="26" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4365,34 +4368,34 @@
         <v>10</v>
       </c>
       <c r="B26">
-        <v>1888.0</v>
+        <v>1987.0</v>
       </c>
       <c r="C26">
-        <v>1987.0</v>
+        <v>2014.0</v>
       </c>
       <c r="D26">
-        <v>2014.0</v>
+        <v>2056.0</v>
       </c>
       <c r="E26">
-        <v>2056.0</v>
+        <v>3529.0</v>
       </c>
       <c r="F26">
-        <v>3529.0</v>
+        <v>4065.0</v>
       </c>
       <c r="G26">
-        <v>4065.0</v>
+        <v>4604.0</v>
       </c>
       <c r="H26">
-        <v>4604.0</v>
+        <v>5022.0</v>
       </c>
       <c r="I26">
-        <v>5022.0</v>
+        <v>4985.0</v>
       </c>
       <c r="J26">
-        <v>4985.0</v>
+        <v>5242.0</v>
       </c>
       <c r="K26">
-        <v>5242.0</v>
+        <v>5560.0</v>
       </c>
     </row>
     <row r="27" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4400,34 +4403,34 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="C27">
-        <v>32.0</v>
+        <v>52.0</v>
       </c>
       <c r="D27">
-        <v>52.0</v>
+        <v>198.0</v>
       </c>
       <c r="E27">
-        <v>198.0</v>
+        <v>924.0</v>
       </c>
       <c r="F27">
-        <v>924.0</v>
+        <v>637.0</v>
       </c>
       <c r="G27">
-        <v>637.0</v>
+        <v>784.0</v>
       </c>
       <c r="H27">
-        <v>784.0</v>
+        <v>779.0</v>
       </c>
       <c r="I27">
-        <v>779.0</v>
+        <v>778.0</v>
       </c>
       <c r="J27">
-        <v>778.0</v>
+        <v>796.0</v>
       </c>
       <c r="K27">
-        <v>796.0</v>
+        <v>1227.0</v>
       </c>
     </row>
     <row r="28" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4435,34 +4438,34 @@
         <v>12</v>
       </c>
       <c r="B28">
-        <v>31840.0</v>
+        <v>34513.0</v>
       </c>
       <c r="C28">
-        <v>34513.0</v>
+        <v>34092.0</v>
       </c>
       <c r="D28">
-        <v>34092.0</v>
+        <v>41563.0</v>
       </c>
       <c r="E28">
-        <v>41563.0</v>
+        <v>42248.0</v>
       </c>
       <c r="F28">
-        <v>42248.0</v>
+        <v>43760.0</v>
       </c>
       <c r="G28">
-        <v>43760.0</v>
+        <v>51687.0</v>
       </c>
       <c r="H28">
-        <v>51687.0</v>
+        <v>56907.0</v>
       </c>
       <c r="I28">
-        <v>56907.0</v>
+        <v>61997.0</v>
       </c>
       <c r="J28">
-        <v>61997.0</v>
+        <v>65331.0</v>
       </c>
       <c r="K28">
-        <v>65331.0</v>
+        <v>65487.0</v>
       </c>
     </row>
     <row r="29" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4470,34 +4473,34 @@
         <v>13</v>
       </c>
       <c r="B29">
-        <v>7502.0</v>
+        <v>8156.0</v>
       </c>
       <c r="C29">
-        <v>8156.0</v>
+        <v>8212.0</v>
       </c>
       <c r="D29">
-        <v>8212.0</v>
+        <v>10001.0</v>
       </c>
       <c r="E29">
-        <v>10001.0</v>
+        <v>9801.0</v>
       </c>
       <c r="F29">
-        <v>9801.0</v>
+        <v>11198.0</v>
       </c>
       <c r="G29">
-        <v>11198.0</v>
+        <v>13238.0</v>
       </c>
       <c r="H29">
-        <v>13238.0</v>
+        <v>14604.0</v>
       </c>
       <c r="I29">
-        <v>14604.0</v>
+        <v>15898.0</v>
       </c>
       <c r="J29">
-        <v>15898.0</v>
+        <v>16534.0</v>
       </c>
       <c r="K29">
-        <v>16534.0</v>
+        <v>16033.0</v>
       </c>
     </row>
     <row r="30" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4505,34 +4508,34 @@
         <v>14</v>
       </c>
       <c r="B30">
-        <v>24270.0</v>
+        <v>26289.0</v>
       </c>
       <c r="C30">
-        <v>26289.0</v>
+        <v>25826.0</v>
       </c>
       <c r="D30">
-        <v>25826.0</v>
+        <v>31472.0</v>
       </c>
       <c r="E30">
-        <v>31472.0</v>
+        <v>32340.0</v>
       </c>
       <c r="F30">
-        <v>32340.0</v>
+        <v>32430.0</v>
       </c>
       <c r="G30">
-        <v>32430.0</v>
+        <v>38327.0</v>
       </c>
       <c r="H30">
-        <v>38327.0</v>
+        <v>42147.0</v>
       </c>
       <c r="I30">
-        <v>42147.0</v>
+        <v>45908.0</v>
       </c>
       <c r="J30">
-        <v>45908.0</v>
+        <v>48553.0</v>
       </c>
       <c r="K30">
-        <v>48553.0</v>
+        <v>49210.0</v>
       </c>
     </row>
     <row r="31" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4540,34 +4543,34 @@
         <v>70</v>
       </c>
       <c r="B31">
-        <v>8569.5</v>
+        <v>9259.0</v>
       </c>
       <c r="C31">
-        <v>9259.0</v>
+        <v>9550.0</v>
       </c>
       <c r="D31">
-        <v>9550.0</v>
+        <v>11250.0</v>
       </c>
       <c r="E31">
-        <v>11250.0</v>
+        <v>27375.0</v>
       </c>
       <c r="F31">
-        <v>27375.0</v>
+        <v>14060.0</v>
       </c>
       <c r="G31">
-        <v>14060.0</v>
+        <v>15738.0</v>
       </c>
       <c r="H31">
-        <v>15738.0</v>
+        <v>42090.0</v>
       </c>
       <c r="I31">
-        <v>42090.0</v>
+        <v>26426.0</v>
       </c>
       <c r="J31">
-        <v>26426.0</v>
+        <v>45612.0</v>
       </c>
       <c r="K31">
-        <v>45612.0</v>
+        <v>39820.0</v>
       </c>
     </row>
     <row r="32" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -4602,34 +4605,34 @@
         <v>38</v>
       </c>
       <c r="B41" s="16">
-        <v>45199.0</v>
+        <v>45382.0</v>
       </c>
       <c r="C41" s="16">
-        <v>45291.0</v>
+        <v>45473.0</v>
       </c>
       <c r="D41" s="16">
-        <v>45382.0</v>
+        <v>45565.0</v>
       </c>
       <c r="E41" s="16">
-        <v>45473.0</v>
+        <v>45657.0</v>
       </c>
       <c r="F41" s="16">
-        <v>45565.0</v>
+        <v>45747.0</v>
       </c>
       <c r="G41" s="16">
-        <v>45657.0</v>
+        <v>45838.0</v>
       </c>
       <c r="H41" s="16">
-        <v>45747.0</v>
+        <v>45930.0</v>
       </c>
       <c r="I41" s="16">
-        <v>45838.0</v>
+        <v>46022.0</v>
       </c>
       <c r="J41" s="16">
-        <v>45930.0</v>
+        <v>46112.0</v>
       </c>
       <c r="K41" s="16">
-        <v>46022.0</v>
+        <v>46203.0</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4637,34 +4640,34 @@
         <v>6</v>
       </c>
       <c r="B42">
-        <v>59692.0</v>
+        <v>61237.0</v>
       </c>
       <c r="C42">
-        <v>60583.0</v>
+        <v>62613.0</v>
       </c>
       <c r="D42">
-        <v>61237.0</v>
+        <v>64259.0</v>
       </c>
       <c r="E42">
-        <v>62613.0</v>
+        <v>63973.0</v>
       </c>
       <c r="F42">
-        <v>64259.0</v>
+        <v>64479.0</v>
       </c>
       <c r="G42">
-        <v>63973.0</v>
+        <v>63437.0</v>
       </c>
       <c r="H42">
-        <v>64479.0</v>
+        <v>65799.0</v>
       </c>
       <c r="I42">
-        <v>63437.0</v>
+        <v>67087.0</v>
       </c>
       <c r="J42">
-        <v>65799.0</v>
+        <v>70698.0</v>
       </c>
       <c r="K42">
-        <v>67087.0</v>
+        <v>72275.0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4672,34 +4675,34 @@
         <v>7</v>
       </c>
       <c r="B43">
-        <v>43946.0</v>
+        <v>44073.0</v>
       </c>
       <c r="C43">
-        <v>44195.0</v>
+        <v>45951.0</v>
       </c>
       <c r="D43">
-        <v>44073.0</v>
+        <v>47528.0</v>
       </c>
       <c r="E43">
-        <v>45951.0</v>
+        <v>46939.0</v>
       </c>
       <c r="F43">
-        <v>47528.0</v>
+        <v>47499.0</v>
       </c>
       <c r="G43">
-        <v>46939.0</v>
+        <v>46562.0</v>
       </c>
       <c r="H43">
-        <v>47499.0</v>
+        <v>47821.0</v>
       </c>
       <c r="I43">
-        <v>46562.0</v>
+        <v>48818.0</v>
       </c>
       <c r="J43">
-        <v>47821.0</v>
+        <v>51422.0</v>
       </c>
       <c r="K43">
-        <v>48818.0</v>
+        <v>53719.0</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4707,34 +4710,34 @@
         <v>9</v>
       </c>
       <c r="B44">
-        <v>1006.0</v>
+        <v>1157.0</v>
       </c>
       <c r="C44">
-        <v>-96.0</v>
+        <v>962.0</v>
       </c>
       <c r="D44">
-        <v>1157.0</v>
+        <v>729.0</v>
       </c>
       <c r="E44">
-        <v>962.0</v>
+        <v>1243.0</v>
       </c>
       <c r="F44">
-        <v>729.0</v>
+        <v>1028.0</v>
       </c>
       <c r="G44">
-        <v>1243.0</v>
+        <v>1660.0</v>
       </c>
       <c r="H44">
-        <v>1028.0</v>
+        <v>-268.0</v>
       </c>
       <c r="I44">
-        <v>1660.0</v>
+        <v>-2273.0</v>
       </c>
       <c r="J44">
-        <v>-268.0</v>
+        <v>757.0</v>
       </c>
       <c r="K44">
-        <v>-2273.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4742,34 +4745,34 @@
         <v>10</v>
       </c>
       <c r="B45">
-        <v>1263.0</v>
+        <v>1246.0</v>
       </c>
       <c r="C45">
-        <v>1233.0</v>
+        <v>1220.0</v>
       </c>
       <c r="D45">
-        <v>1246.0</v>
+        <v>1266.0</v>
       </c>
       <c r="E45">
-        <v>1220.0</v>
+        <v>1377.0</v>
       </c>
       <c r="F45">
-        <v>1266.0</v>
+        <v>1379.0</v>
       </c>
       <c r="G45">
-        <v>1377.0</v>
+        <v>1361.0</v>
       </c>
       <c r="H45">
-        <v>1379.0</v>
+        <v>1413.0</v>
       </c>
       <c r="I45">
-        <v>1361.0</v>
+        <v>1380.0</v>
       </c>
       <c r="J45">
-        <v>1413.0</v>
+        <v>1406.0</v>
       </c>
       <c r="K45">
-        <v>1380.0</v>
+        <v>1239.0</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4777,34 +4780,34 @@
         <v>11</v>
       </c>
       <c r="B46">
-        <v>159.0</v>
+        <v>226.0</v>
       </c>
       <c r="C46">
-        <v>230.0</v>
+        <v>173.0</v>
       </c>
       <c r="D46">
-        <v>226.0</v>
+        <v>162.0</v>
       </c>
       <c r="E46">
-        <v>173.0</v>
+        <v>234.0</v>
       </c>
       <c r="F46">
-        <v>162.0</v>
+        <v>227.0</v>
       </c>
       <c r="G46">
-        <v>234.0</v>
+        <v>195.0</v>
       </c>
       <c r="H46">
-        <v>227.0</v>
+        <v>229.0</v>
       </c>
       <c r="I46">
-        <v>195.0</v>
+        <v>538.0</v>
       </c>
       <c r="J46">
-        <v>229.0</v>
+        <v>265.0</v>
       </c>
       <c r="K46">
-        <v>538.0</v>
+        <v>273.0</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4812,34 +4815,34 @@
         <v>12</v>
       </c>
       <c r="B47">
-        <v>15330.0</v>
+        <v>16849.0</v>
       </c>
       <c r="C47">
-        <v>14829.0</v>
+        <v>16231.0</v>
       </c>
       <c r="D47">
-        <v>16849.0</v>
+        <v>16032.0</v>
       </c>
       <c r="E47">
-        <v>16231.0</v>
+        <v>16666.0</v>
       </c>
       <c r="F47">
-        <v>16032.0</v>
+        <v>16402.0</v>
       </c>
       <c r="G47">
-        <v>16666.0</v>
+        <v>16979.0</v>
       </c>
       <c r="H47">
-        <v>16402.0</v>
+        <v>16068.0</v>
       </c>
       <c r="I47">
-        <v>16979.0</v>
+        <v>14078.0</v>
       </c>
       <c r="J47">
-        <v>16068.0</v>
+        <v>18362.0</v>
       </c>
       <c r="K47">
-        <v>14078.0</v>
+        <v>17944.0</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4847,34 +4850,34 @@
         <v>13</v>
       </c>
       <c r="B48">
-        <v>3950.0</v>
+        <v>4347.0</v>
       </c>
       <c r="C48">
-        <v>3732.0</v>
+        <v>4126.0</v>
       </c>
       <c r="D48">
-        <v>4347.0</v>
+        <v>4077.0</v>
       </c>
       <c r="E48">
-        <v>4126.0</v>
+        <v>4222.0</v>
       </c>
       <c r="F48">
-        <v>4077.0</v>
+        <v>4109.0</v>
       </c>
       <c r="G48">
-        <v>4222.0</v>
+        <v>4160.0</v>
       </c>
       <c r="H48">
-        <v>4109.0</v>
+        <v>3937.0</v>
       </c>
       <c r="I48">
-        <v>4160.0</v>
+        <v>3358.0</v>
       </c>
       <c r="J48">
-        <v>3937.0</v>
+        <v>4578.0</v>
       </c>
       <c r="K48">
-        <v>3358.0</v>
+        <v>4524.0</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4882,34 +4885,34 @@
         <v>14</v>
       </c>
       <c r="B49">
-        <v>11342.0</v>
+        <v>12434.0</v>
       </c>
       <c r="C49">
-        <v>11058.0</v>
+        <v>12040.0</v>
       </c>
       <c r="D49">
-        <v>12434.0</v>
+        <v>11909.0</v>
       </c>
       <c r="E49">
-        <v>12040.0</v>
+        <v>12380.0</v>
       </c>
       <c r="F49">
-        <v>11909.0</v>
+        <v>12224.0</v>
       </c>
       <c r="G49">
-        <v>12380.0</v>
+        <v>12760.0</v>
       </c>
       <c r="H49">
-        <v>12224.0</v>
+        <v>12075.0</v>
       </c>
       <c r="I49">
-        <v>12760.0</v>
+        <v>10657.0</v>
       </c>
       <c r="J49">
-        <v>12075.0</v>
+        <v>13718.0</v>
       </c>
       <c r="K49">
-        <v>10657.0</v>
+        <v>13349.0</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -4917,34 +4920,34 @@
         <v>8</v>
       </c>
       <c r="B50">
-        <v>15746.0</v>
+        <v>17164.0</v>
       </c>
       <c r="C50">
-        <v>16388.0</v>
+        <v>16662.0</v>
       </c>
       <c r="D50">
-        <v>17164.0</v>
+        <v>16731.0</v>
       </c>
       <c r="E50">
-        <v>16662.0</v>
+        <v>17034.0</v>
       </c>
       <c r="F50">
-        <v>16731.0</v>
+        <v>16980.0</v>
       </c>
       <c r="G50">
-        <v>17034.0</v>
+        <v>16875.0</v>
       </c>
       <c r="H50">
-        <v>16980.0</v>
+        <v>17978.0</v>
       </c>
       <c r="I50">
-        <v>16875.0</v>
+        <v>18269.0</v>
       </c>
       <c r="J50">
-        <v>17978.0</v>
+        <v>19276.0</v>
       </c>
       <c r="K50">
-        <v>18269.0</v>
+        <v>18556.0</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -4969,34 +4972,34 @@
         <v>38</v>
       </c>
       <c r="B56" s="16">
-        <v>42460.0</v>
+        <v>42825.0</v>
       </c>
       <c r="C56" s="16">
-        <v>42825.0</v>
+        <v>43190.0</v>
       </c>
       <c r="D56" s="16">
-        <v>43190.0</v>
+        <v>43555.0</v>
       </c>
       <c r="E56" s="16">
-        <v>43555.0</v>
+        <v>43921.0</v>
       </c>
       <c r="F56" s="16">
-        <v>43921.0</v>
+        <v>44286.0</v>
       </c>
       <c r="G56" s="16">
-        <v>44286.0</v>
+        <v>44651.0</v>
       </c>
       <c r="H56" s="16">
-        <v>44651.0</v>
+        <v>45016.0</v>
       </c>
       <c r="I56" s="16">
-        <v>45016.0</v>
+        <v>45382.0</v>
       </c>
       <c r="J56" s="16">
-        <v>45382.0</v>
+        <v>45747.0</v>
       </c>
       <c r="K56" s="16">
-        <v>45747.0</v>
+        <v>46112.0</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -5007,25 +5010,25 @@
         <v>197.0</v>
       </c>
       <c r="C57">
-        <v>197.0</v>
+        <v>191.0</v>
       </c>
       <c r="D57">
-        <v>191.0</v>
+        <v>375.0</v>
       </c>
       <c r="E57">
         <v>375.0</v>
       </c>
       <c r="F57">
-        <v>375.0</v>
+        <v>370.0</v>
       </c>
       <c r="G57">
-        <v>370.0</v>
+        <v>366.0</v>
       </c>
       <c r="H57">
         <v>366.0</v>
       </c>
       <c r="I57">
-        <v>366.0</v>
+        <v>362.0</v>
       </c>
       <c r="J57">
         <v>362.0</v>
@@ -5039,34 +5042,34 @@
         <v>25</v>
       </c>
       <c r="B58">
-        <v>70875.0</v>
+        <v>86017.0</v>
       </c>
       <c r="C58">
-        <v>86017.0</v>
+        <v>84937.0</v>
       </c>
       <c r="D58">
-        <v>84937.0</v>
+        <v>89071.0</v>
       </c>
       <c r="E58">
-        <v>89071.0</v>
+        <v>83751.0</v>
       </c>
       <c r="F58">
-        <v>83751.0</v>
+        <v>86063.0</v>
       </c>
       <c r="G58">
-        <v>86063.0</v>
+        <v>88773.0</v>
       </c>
       <c r="H58">
-        <v>88773.0</v>
+        <v>90058.0</v>
       </c>
       <c r="I58">
-        <v>90058.0</v>
+        <v>90127.0</v>
       </c>
       <c r="J58">
-        <v>90127.0</v>
+        <v>94394.0</v>
       </c>
       <c r="K58">
-        <v>94394.0</v>
+        <v>106878.0</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -5074,34 +5077,34 @@
         <v>71</v>
       </c>
       <c r="B59">
-        <v>245.0</v>
+        <v>289.0</v>
       </c>
       <c r="C59">
-        <v>289.0</v>
+        <v>247.0</v>
       </c>
       <c r="D59">
-        <v>247.0</v>
+        <v>62.0</v>
       </c>
       <c r="E59">
-        <v>62.0</v>
+        <v>8174.0</v>
       </c>
       <c r="F59">
-        <v>8174.0</v>
+        <v>7795.0</v>
       </c>
       <c r="G59">
-        <v>7795.0</v>
+        <v>7818.0</v>
       </c>
       <c r="H59">
-        <v>7818.0</v>
+        <v>7688.0</v>
       </c>
       <c r="I59">
-        <v>7688.0</v>
+        <v>8021.0</v>
       </c>
       <c r="J59">
-        <v>8021.0</v>
+        <v>9392.0</v>
       </c>
       <c r="K59">
-        <v>9392.0</v>
+        <v>11283.0</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -5109,34 +5112,34 @@
         <v>72</v>
       </c>
       <c r="B60">
-        <v>16974.0</v>
+        <v>15830.0</v>
       </c>
       <c r="C60">
-        <v>15830.0</v>
+        <v>19751.0</v>
       </c>
       <c r="D60">
-        <v>19751.0</v>
+        <v>24393.0</v>
       </c>
       <c r="E60">
-        <v>24393.0</v>
+        <v>27827.0</v>
       </c>
       <c r="F60">
-        <v>27827.0</v>
+        <v>35764.0</v>
       </c>
       <c r="G60">
-        <v>35764.0</v>
+        <v>43967.0</v>
       </c>
       <c r="H60">
-        <v>43967.0</v>
+        <v>44747.0</v>
       </c>
       <c r="I60">
-        <v>44747.0</v>
+        <v>46962.0</v>
       </c>
       <c r="J60">
-        <v>46962.0</v>
+        <v>54501.0</v>
       </c>
       <c r="K60">
-        <v>54501.0</v>
+        <v>62644.0</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5144,34 +5147,34 @@
         <v>26</v>
       </c>
       <c r="B61">
-        <v>88291.0</v>
+        <v>102333.0</v>
       </c>
       <c r="C61">
-        <v>102333.0</v>
+        <v>105126.0</v>
       </c>
       <c r="D61">
-        <v>105126.0</v>
+        <v>113901.0</v>
       </c>
       <c r="E61">
-        <v>113901.0</v>
+        <v>120127.0</v>
       </c>
       <c r="F61">
-        <v>120127.0</v>
+        <v>129992.0</v>
       </c>
       <c r="G61">
-        <v>129992.0</v>
+        <v>140924.0</v>
       </c>
       <c r="H61">
-        <v>140924.0</v>
+        <v>142859.0</v>
       </c>
       <c r="I61">
-        <v>142859.0</v>
+        <v>145472.0</v>
       </c>
       <c r="J61">
-        <v>145472.0</v>
+        <v>158649.0</v>
       </c>
       <c r="K61">
-        <v>158649.0</v>
+        <v>181167.0</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -5179,34 +5182,34 @@
         <v>27</v>
       </c>
       <c r="B62">
-        <v>11774.0</v>
+        <v>11701.0</v>
       </c>
       <c r="C62">
-        <v>11701.0</v>
+        <v>11973.0</v>
       </c>
       <c r="D62">
-        <v>11973.0</v>
+        <v>12290.0</v>
       </c>
       <c r="E62">
-        <v>12290.0</v>
+        <v>20928.0</v>
       </c>
       <c r="F62">
-        <v>20928.0</v>
+        <v>21021.0</v>
       </c>
       <c r="G62">
-        <v>21021.0</v>
+        <v>21298.0</v>
       </c>
       <c r="H62">
-        <v>21298.0</v>
+        <v>20515.0</v>
       </c>
       <c r="I62">
-        <v>20515.0</v>
+        <v>19604.0</v>
       </c>
       <c r="J62">
-        <v>19604.0</v>
+        <v>23053.0</v>
       </c>
       <c r="K62">
-        <v>23053.0</v>
+        <v>31343.0</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -5214,34 +5217,34 @@
         <v>28</v>
       </c>
       <c r="B63">
-        <v>1670.0</v>
+        <v>1541.0</v>
       </c>
       <c r="C63">
-        <v>1541.0</v>
+        <v>1278.0</v>
       </c>
       <c r="D63">
-        <v>1278.0</v>
+        <v>963.0</v>
       </c>
       <c r="E63">
-        <v>963.0</v>
+        <v>906.0</v>
       </c>
       <c r="F63">
-        <v>906.0</v>
+        <v>926.0</v>
       </c>
       <c r="G63">
-        <v>926.0</v>
+        <v>1205.0</v>
       </c>
       <c r="H63">
-        <v>1205.0</v>
+        <v>1234.0</v>
       </c>
       <c r="I63">
-        <v>1234.0</v>
+        <v>1564.0</v>
       </c>
       <c r="J63">
-        <v>1564.0</v>
+        <v>1546.0</v>
       </c>
       <c r="K63">
-        <v>1546.0</v>
+        <v>2665.0</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -5249,34 +5252,34 @@
         <v>29</v>
       </c>
       <c r="B64">
-        <v>22822.0</v>
+        <v>41980.0</v>
       </c>
       <c r="C64">
-        <v>41980.0</v>
+        <v>36008.0</v>
       </c>
       <c r="D64">
-        <v>36008.0</v>
+        <v>29330.0</v>
       </c>
       <c r="E64">
-        <v>29330.0</v>
+        <v>26356.0</v>
       </c>
       <c r="F64">
-        <v>26356.0</v>
+        <v>29373.0</v>
       </c>
       <c r="G64">
-        <v>29373.0</v>
+        <v>30485.0</v>
       </c>
       <c r="H64">
-        <v>30485.0</v>
+        <v>37163.0</v>
       </c>
       <c r="I64">
-        <v>37163.0</v>
+        <v>31762.0</v>
       </c>
       <c r="J64">
-        <v>31762.0</v>
+        <v>30964.0</v>
       </c>
       <c r="K64">
-        <v>30964.0</v>
+        <v>33988.0</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
@@ -5284,34 +5287,34 @@
         <v>73</v>
       </c>
       <c r="B65">
-        <v>52025.0</v>
+        <v>47111.0</v>
       </c>
       <c r="C65">
-        <v>47111.0</v>
+        <v>55867.0</v>
       </c>
       <c r="D65">
-        <v>55867.0</v>
+        <v>71318.0</v>
       </c>
       <c r="E65">
-        <v>71318.0</v>
+        <v>71937.0</v>
       </c>
       <c r="F65">
-        <v>71937.0</v>
+        <v>78672.0</v>
       </c>
       <c r="G65">
-        <v>78672.0</v>
+        <v>87936.0</v>
       </c>
       <c r="H65">
-        <v>87936.0</v>
+        <v>83947.0</v>
       </c>
       <c r="I65">
-        <v>83947.0</v>
+        <v>92542.0</v>
       </c>
       <c r="J65">
-        <v>92542.0</v>
+        <v>103086.0</v>
       </c>
       <c r="K65">
-        <v>103086.0</v>
+        <v>113171.0</v>
       </c>
     </row>
     <row r="66" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5319,34 +5322,34 @@
         <v>26</v>
       </c>
       <c r="B66">
-        <v>88291.0</v>
+        <v>102333.0</v>
       </c>
       <c r="C66">
-        <v>102333.0</v>
+        <v>105126.0</v>
       </c>
       <c r="D66">
-        <v>105126.0</v>
+        <v>113901.0</v>
       </c>
       <c r="E66">
-        <v>113901.0</v>
+        <v>120127.0</v>
       </c>
       <c r="F66">
-        <v>120127.0</v>
+        <v>129992.0</v>
       </c>
       <c r="G66">
-        <v>129992.0</v>
+        <v>140924.0</v>
       </c>
       <c r="H66">
-        <v>140924.0</v>
+        <v>142859.0</v>
       </c>
       <c r="I66">
-        <v>142859.0</v>
+        <v>145472.0</v>
       </c>
       <c r="J66">
-        <v>145472.0</v>
+        <v>158649.0</v>
       </c>
       <c r="K66">
-        <v>158649.0</v>
+        <v>181167.0</v>
       </c>
     </row>
     <row r="67" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5354,34 +5357,34 @@
         <v>78</v>
       </c>
       <c r="B67">
-        <v>24073.0</v>
+        <v>22617.0</v>
       </c>
       <c r="C67">
-        <v>22617.0</v>
+        <v>24943.0</v>
       </c>
       <c r="D67">
-        <v>24943.0</v>
+        <v>27346.0</v>
       </c>
       <c r="E67">
-        <v>27346.0</v>
+        <v>30532.0</v>
       </c>
       <c r="F67">
-        <v>30532.0</v>
+        <v>30079.0</v>
       </c>
       <c r="G67">
-        <v>30079.0</v>
+        <v>41810.0</v>
       </c>
       <c r="H67">
-        <v>41810.0</v>
+        <v>49954.0</v>
       </c>
       <c r="I67">
-        <v>49954.0</v>
+        <v>53577.0</v>
       </c>
       <c r="J67">
-        <v>53577.0</v>
+        <v>59046.0</v>
       </c>
       <c r="K67">
-        <v>59046.0</v>
+        <v>67714.0</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
@@ -5389,34 +5392,34 @@
         <v>45</v>
       </c>
       <c r="B68">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="C68">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="D68">
-        <v>26.0</v>
+        <v>10.0</v>
       </c>
       <c r="E68">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F68">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G68">
-        <v>8.0</v>
+        <v>20.0</v>
       </c>
       <c r="H68">
-        <v>20.0</v>
+        <v>28.0</v>
       </c>
       <c r="I68">
         <v>28.0</v>
       </c>
       <c r="J68">
-        <v>28.0</v>
+        <v>21.0</v>
       </c>
       <c r="K68">
-        <v>21.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
@@ -5424,34 +5427,34 @@
         <v>87</v>
       </c>
       <c r="B69">
-        <v>6788.0</v>
+        <v>4149.0</v>
       </c>
       <c r="C69">
-        <v>4149.0</v>
+        <v>7161.0</v>
       </c>
       <c r="D69">
-        <v>7161.0</v>
+        <v>12848.0</v>
       </c>
       <c r="E69">
-        <v>12848.0</v>
+        <v>9666.0</v>
       </c>
       <c r="F69">
-        <v>9666.0</v>
+        <v>9329.0</v>
       </c>
       <c r="G69">
-        <v>9329.0</v>
+        <v>18221.0</v>
       </c>
       <c r="H69">
-        <v>18221.0</v>
+        <v>11032.0</v>
       </c>
       <c r="I69">
-        <v>11032.0</v>
+        <v>13286.0</v>
       </c>
       <c r="J69">
-        <v>13286.0</v>
+        <v>15463.0</v>
       </c>
       <c r="K69">
-        <v>15463.0</v>
+        <v>12908.0</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
@@ -5462,25 +5465,25 @@
         <v>1970427941.0</v>
       </c>
       <c r="C70">
-        <v>1970427941.0</v>
+        <v>1914287591.0</v>
       </c>
       <c r="D70">
-        <v>1914287591.0</v>
+        <v>3752384706.0</v>
       </c>
       <c r="E70">
         <v>3752384706.0</v>
       </c>
       <c r="F70">
-        <v>3752384706.0</v>
+        <v>3699051373.0</v>
       </c>
       <c r="G70">
-        <v>3699051373.0</v>
+        <v>3659051373.0</v>
       </c>
       <c r="H70">
         <v>3659051373.0</v>
       </c>
       <c r="I70">
-        <v>3659051373.0</v>
+        <v>3618087518.0</v>
       </c>
       <c r="J70">
         <v>3618087518.0</v>
@@ -5557,34 +5560,34 @@
         <v>38</v>
       </c>
       <c r="B81" s="16">
-        <v>42460.0</v>
+        <v>42825.0</v>
       </c>
       <c r="C81" s="16">
-        <v>42825.0</v>
+        <v>43190.0</v>
       </c>
       <c r="D81" s="16">
-        <v>43190.0</v>
+        <v>43555.0</v>
       </c>
       <c r="E81" s="16">
-        <v>43555.0</v>
+        <v>43921.0</v>
       </c>
       <c r="F81" s="16">
-        <v>43921.0</v>
+        <v>44286.0</v>
       </c>
       <c r="G81" s="16">
-        <v>44286.0</v>
+        <v>44651.0</v>
       </c>
       <c r="H81" s="16">
-        <v>44651.0</v>
+        <v>45016.0</v>
       </c>
       <c r="I81" s="16">
-        <v>45016.0</v>
+        <v>45382.0</v>
       </c>
       <c r="J81" s="16">
-        <v>45382.0</v>
+        <v>45747.0</v>
       </c>
       <c r="K81" s="16">
-        <v>45747.0</v>
+        <v>46112.0</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5592,34 +5595,34 @@
         <v>32</v>
       </c>
       <c r="B82">
-        <v>19109.0</v>
+        <v>25223.0</v>
       </c>
       <c r="C82">
-        <v>25223.0</v>
+        <v>25067.0</v>
       </c>
       <c r="D82">
-        <v>25067.0</v>
+        <v>28593.0</v>
       </c>
       <c r="E82">
-        <v>28593.0</v>
+        <v>32369.0</v>
       </c>
       <c r="F82">
-        <v>32369.0</v>
+        <v>38802.0</v>
       </c>
       <c r="G82">
-        <v>38802.0</v>
+        <v>39949.0</v>
       </c>
       <c r="H82">
-        <v>39949.0</v>
+        <v>41965.0</v>
       </c>
       <c r="I82">
-        <v>41965.0</v>
+        <v>44338.0</v>
       </c>
       <c r="J82">
-        <v>44338.0</v>
+        <v>48908.0</v>
       </c>
       <c r="K82">
-        <v>48908.0</v>
+        <v>52094.0</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5627,34 +5630,34 @@
         <v>33</v>
       </c>
       <c r="B83">
-        <v>-5010.0</v>
+        <v>-16895.0</v>
       </c>
       <c r="C83">
-        <v>-16895.0</v>
+        <v>3104.0</v>
       </c>
       <c r="D83">
-        <v>3104.0</v>
+        <v>1645.0</v>
       </c>
       <c r="E83">
-        <v>1645.0</v>
+        <v>8968.0</v>
       </c>
       <c r="F83">
-        <v>8968.0</v>
+        <v>-7956.0</v>
       </c>
       <c r="G83">
-        <v>-7956.0</v>
+        <v>-738.0</v>
       </c>
       <c r="H83">
-        <v>-738.0</v>
+        <v>548.0</v>
       </c>
       <c r="I83">
-        <v>548.0</v>
+        <v>6091.0</v>
       </c>
       <c r="J83">
-        <v>6091.0</v>
+        <v>-2144.0</v>
       </c>
       <c r="K83">
-        <v>-2144.0</v>
+        <v>-11886.0</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5662,34 +5665,34 @@
         <v>34</v>
       </c>
       <c r="B84">
-        <v>-9666.0</v>
+        <v>-11026.0</v>
       </c>
       <c r="C84">
-        <v>-11026.0</v>
+        <v>-26885.0</v>
       </c>
       <c r="D84">
-        <v>-26885.0</v>
+        <v>-27897.0</v>
       </c>
       <c r="E84">
-        <v>-27897.0</v>
+        <v>-39915.0</v>
       </c>
       <c r="F84">
-        <v>-39915.0</v>
+        <v>-32634.0</v>
       </c>
       <c r="G84">
-        <v>-32634.0</v>
+        <v>-33581.0</v>
       </c>
       <c r="H84">
-        <v>-33581.0</v>
+        <v>-47878.0</v>
       </c>
       <c r="I84">
-        <v>-47878.0</v>
+        <v>-48536.0</v>
       </c>
       <c r="J84">
-        <v>-48536.0</v>
+        <v>-47438.0</v>
       </c>
       <c r="K84">
-        <v>-47438.0</v>
+        <v>-42133.0</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5697,34 +5700,34 @@
         <v>35</v>
       </c>
       <c r="B85">
-        <v>4433.0</v>
+        <v>-2698.0</v>
       </c>
       <c r="C85">
-        <v>-2698.0</v>
+        <v>1286.0</v>
       </c>
       <c r="D85">
-        <v>1286.0</v>
+        <v>2341.0</v>
       </c>
       <c r="E85">
-        <v>2341.0</v>
+        <v>1422.0</v>
       </c>
       <c r="F85">
-        <v>1422.0</v>
+        <v>-1788.0</v>
       </c>
       <c r="G85">
-        <v>-1788.0</v>
+        <v>5630.0</v>
       </c>
       <c r="H85">
-        <v>5630.0</v>
+        <v>-5365.0</v>
       </c>
       <c r="I85">
-        <v>-5365.0</v>
+        <v>1893.0</v>
       </c>
       <c r="J85">
-        <v>1893.0</v>
+        <v>-674.0</v>
       </c>
       <c r="K85">
-        <v>-674.0</v>
+        <v>-1925.0</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -5744,34 +5747,34 @@
         <v>77</v>
       </c>
       <c r="B90">
-        <v>1260.15</v>
+        <v>1215.9</v>
       </c>
       <c r="C90">
-        <v>1215.9</v>
+        <v>1424.58</v>
       </c>
       <c r="D90">
-        <v>1424.58</v>
+        <v>2001.65</v>
       </c>
       <c r="E90">
-        <v>2001.65</v>
+        <v>1826.1</v>
       </c>
       <c r="F90">
-        <v>1826.1</v>
+        <v>3177.85</v>
       </c>
       <c r="G90">
-        <v>3177.85</v>
+        <v>3739.95</v>
       </c>
       <c r="H90">
-        <v>3739.95</v>
+        <v>3205.9</v>
       </c>
       <c r="I90">
-        <v>3205.9</v>
+        <v>3876.3</v>
       </c>
       <c r="J90">
-        <v>3876.3</v>
+        <v>3606.15</v>
       </c>
       <c r="K90">
-        <v>3606.15</v>
+        <v>2358.9</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5787,25 +5790,25 @@
         <v>394.09</v>
       </c>
       <c r="C93" s="31">
-        <v>394.09</v>
+        <v>382.86</v>
       </c>
       <c r="D93" s="31">
-        <v>382.86</v>
+        <v>375.24</v>
       </c>
       <c r="E93" s="31">
         <v>375.24</v>
       </c>
       <c r="F93" s="31">
-        <v>375.24</v>
+        <v>369.91</v>
       </c>
       <c r="G93" s="31">
-        <v>369.91</v>
+        <v>365.91</v>
       </c>
       <c r="H93" s="31">
         <v>365.91</v>
       </c>
       <c r="I93" s="31">
-        <v>365.91</v>
+        <v>361.81</v>
       </c>
       <c r="J93" s="31">
         <v>361.81</v>
